--- a/src/uploads/BillTemplate.xlsx
+++ b/src/uploads/BillTemplate.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66ABF8D9-2781-DE45-8AC6-51836E388D25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28120" windowHeight="14280" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="14840" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="TK" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="WpsReserved_CellImgList" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet name="New Data Sheet" sheetId="4" r:id="rId4"/>
+    <sheet name="TK" sheetId="2" state="hidden" r:id="rId1"/>
+    <sheet name="WpsReserved_CellImgList" sheetId="3" state="veryHidden" r:id="rId2"/>
+    <sheet name="New Data Sheet" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>店铺名称</t>
   </si>
@@ -138,39 +127,6 @@
   </si>
   <si>
     <t>订单视频</t>
-  </si>
-  <si>
-    <t>szpzl.th</t>
-  </si>
-  <si>
-    <t>2404087FXHEQJ9</t>
-  </si>
-  <si>
-    <t>TH-SP-818</t>
-  </si>
-  <si>
-    <t>SZPZ53746</t>
-  </si>
-  <si>
-    <t>เครื่องมือกำจัดกาว LCD</t>
-  </si>
-  <si>
-    <t>关注+加购+下单</t>
-  </si>
-  <si>
-    <t>ทัศนคติการบริการที่ดีการจัดส่งที่รวดเร็วและคุ้มค่า</t>
-  </si>
-  <si>
-    <t>2404087G46MDET</t>
-  </si>
-  <si>
-    <t>TH-SP-819</t>
-  </si>
-  <si>
-    <t>ลวดซับตะกั่ว</t>
-  </si>
-  <si>
-    <t>คุณภาพดีมากใช้แรงดึง dula อย่างต่อเนื่อง</t>
   </si>
   <si>
     <t>单链接模板</t>
@@ -426,8 +382,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,50 +473,148 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="48"/>
-      <color rgb="FF333333"/>
-      <name val="helvetica"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="72"/>
-      <color rgb="FF333333"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="48"/>
-      <color rgb="FFEE4D2D"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -570,7 +630,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,12 +651,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -633,23 +879,252 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -687,13 +1162,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -718,320 +1193,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>4001135</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>107315</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="54730650" y="2628900"/>
-          <a:ext cx="4001135" cy="3891915"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>3686175</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3566160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="61293375" y="2628900"/>
-          <a:ext cx="3686175" cy="3566160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>3724910</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>3684905</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="54730650" y="6426200"/>
-          <a:ext cx="3724910" cy="3672205"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>3486150</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>3454400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="61293375" y="6426200"/>
-          <a:ext cx="3486150" cy="3441700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>19440525</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3743325</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>2638425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>3540125</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="93530420" y="6372225"/>
-          <a:ext cx="2676525" cy="3581400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>2790825</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>1347470</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>3381375</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="96359345" y="6575425"/>
-          <a:ext cx="4290695" cy="3219450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1286,197 +1506,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="171" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="37.83203125" style="3" customWidth="1"/>
-    <col min="2" max="5" width="62" style="3" customWidth="1"/>
-    <col min="6" max="6" width="50.1640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="59" style="4" customWidth="1"/>
-    <col min="8" max="8" width="67.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="255.6640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="86.1640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="49.6640625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="38.5" style="6" customWidth="1"/>
-    <col min="13" max="13" width="34.5" style="5" customWidth="1"/>
-    <col min="14" max="14" width="45.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="255.6640625" style="7" customWidth="1"/>
-    <col min="16" max="19" width="37.6640625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="29.83203125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="119.83203125" style="3" customWidth="1"/>
-    <col min="22" max="22" width="34.5" style="2" customWidth="1"/>
-    <col min="23" max="23" width="28.83203125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="16" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="16" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21 16381:16384" s="1" customFormat="1" ht="207" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="XFA1" s="8"/>
-      <c r="XFB1" s="8"/>
-      <c r="XFC1" s="8"/>
-      <c r="XFD1" s="8"/>
-    </row>
-    <row r="2" spans="1:21 16381:16384" ht="298" customHeight="1">
-      <c r="A2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="21">
-        <v>243</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="21">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="26"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18">
-        <v>440</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="20"/>
-    </row>
-    <row r="3" spans="1:21 16381:16384" ht="298" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="21">
-        <v>83</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="21">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="26"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18">
-        <v>60</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="20"/>
-    </row>
-    <row r="4" spans="1:21 16381:16384" ht="88">
-      <c r="I4" s="25"/>
-      <c r="J4" s="28"/>
-    </row>
-    <row r="5" spans="1:21 16381:16384" ht="68">
-      <c r="I5" s="29"/>
-      <c r="J5" s="28"/>
-    </row>
-  </sheetData>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:XFD2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="171" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="171" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="37.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.8359375" style="3" customWidth="1"/>
     <col min="3" max="3" width="62" style="3" customWidth="1"/>
     <col min="4" max="4" width="50.1640625" style="3" customWidth="1"/>
     <col min="5" max="5" width="59" style="4" customWidth="1"/>
@@ -1489,15 +1529,15 @@
     <col min="12" max="12" width="19.6640625" style="3" customWidth="1"/>
     <col min="13" max="13" width="255.6640625" style="7" customWidth="1"/>
     <col min="14" max="17" width="37.6640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="119.83203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="29.8359375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="119.8359375" style="3" customWidth="1"/>
     <col min="20" max="20" width="34.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="28.83203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="28.8359375" style="2" customWidth="1"/>
     <col min="22" max="22" width="16" style="2" customWidth="1"/>
     <col min="23" max="16384" width="16" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19 16379:16384" s="1" customFormat="1" ht="207" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="207" customHeight="1" spans="1:16384">
       <c r="A1" s="8"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -1508,7 +1548,7 @@
       <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
@@ -1560,14 +1600,14 @@
       <c r="XFC1" s="8"/>
       <c r="XFD1" s="8"/>
     </row>
-    <row r="2" spans="1:19 16379:16384" ht="298" customHeight="1">
+    <row r="2" ht="298" customHeight="1" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="13">
+        <v>18</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="12">
         <v>1</v>
       </c>
       <c r="D2" s="3">
@@ -1575,64 +1615,68 @@
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="15" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="3" t="e">
-        <f ca="1">_xlfn.DISPIMG("ID_BC765EF371B54463B9E8CD5D6C9D7110",1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I2" s="5" t="e">
-        <f ca="1">_xlfn.DISPIMG("ID_7B9C0CC28D4D44A88522E6AEC9167BA1",1)</f>
-        <v>#NAME?</v>
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f>_xlfn.DISPIMG("ID_BC765EF371B54463B9E8CD5D6C9D7110",1)</f>
+        <v>=DISPIMG("ID_BC765EF371B54463B9E8CD5D6C9D7110",1)</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <f>_xlfn.DISPIMG("ID_7B9C0CC28D4D44A88522E6AEC9167BA1",1)</f>
+        <v>=DISPIMG("ID_7B9C0CC28D4D44A88522E6AEC9167BA1",1)</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="3" t="e">
-        <f ca="1">_xlfn.DISPIMG("ID_0E6103384643409CAF2CC27CECE0D6C2",1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="O2" s="3" t="e">
-        <f ca="1">_xlfn.DISPIMG("ID_0D6DC74696654CB88E01E925D3C39438",1)</f>
-        <v>#NAME?</v>
+        <v>25</v>
+      </c>
+      <c r="N2" s="3" t="str">
+        <f>_xlfn.DISPIMG("ID_0E6103384643409CAF2CC27CECE0D6C2",1)</f>
+        <v>=DISPIMG("ID_0E6103384643409CAF2CC27CECE0D6C2",1)</v>
+      </c>
+      <c r="O2" s="3" t="str">
+        <f>_xlfn.DISPIMG("ID_0D6DC74696654CB88E01E925D3C39438",1)</f>
+        <v>=DISPIMG("ID_0D6DC74696654CB88E01E925D3C39438",1)</v>
       </c>
       <c r="Q2" s="20"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://th.xiapibuy.com/product/105357/21692468610?ADTAG=mydata_productperform_item"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
+  <sheetData/>
+  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
-  <sheetData/>
-  <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -1641,104 +1685,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <v>243</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>243</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>243</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/src/uploads/BillTemplate.xlsx
+++ b/src/uploads/BillTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14840" firstSheet="2" activeTab="2"/>
+    <workbookView windowHeight="15680" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TK" sheetId="2" state="hidden" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>店铺名称</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>买手号</t>
+  </si>
+  <si>
+    <t>客户编码</t>
   </si>
 </sst>
 </file>
@@ -384,8 +387,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -473,6 +476,110 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -481,25 +588,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -511,36 +604,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -551,67 +614,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -630,7 +633,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,12 +672,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -687,157 +708,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -894,11 +891,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -921,8 +948,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -941,186 +968,156 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1675,15 +1672,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -1695,6 +1692,9 @@
       </c>
       <c r="D1" t="s">
         <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
